--- a/tools/_out/groupB_20261021/out/fs/DesignTable_FS2408_SW2.xlsx
+++ b/tools/_out/groupB_20261021/out/fs/DesignTable_FS2408_SW2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF3"/>
+  <dimension ref="A1:AF9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -696,118 +696,838 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>FS2408-24</t>
+          <t>FS2408-04</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.1</v>
+        <v>0.66</v>
       </c>
       <c r="C3" t="n">
-        <v>1.22976</v>
+        <v>0.36373</v>
       </c>
       <c r="D3" t="n">
-        <v>2.13</v>
+        <v>0.63</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7125</v>
+        <v>0.1145</v>
       </c>
       <c r="F3" t="n">
         <v>0.052</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8145</v>
+        <v>0.2165</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.2415</v>
       </c>
       <c r="I3" t="n">
         <v>45</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>0.28125</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4676</v>
+        <v>0.23885</v>
       </c>
       <c r="L3" t="n">
         <v>60</v>
       </c>
       <c r="M3" t="n">
+        <v>0.239</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.08301</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.2786</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.03007</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.01389</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>FS2408-04</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>ORFS Male Plug (male face seal, blind hole), 9/16-18 UN (male O-ring face seal, SAE J1453) (hollow)</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>FS2408</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>plug head</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>9/16-18 UN (male O-ring face seal, SAE J1453)</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>Air-Way FF2408 (s12, double-pass 2026-10-15, parts.air-way.com/api/series/12, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p21 FS2408-04 (ORFS-p021-t02) | MODEL: L24 face -&gt; back face, hex S1 (Air-Way): review table (Air-Way, staged FS table; OMi website list decides the parts); male face-seal end = the straight FSM end library; plug head = hex to a plain flat back face (Brennan FS2408-08 STEP; hex chamfers not modelled); BLIND HOLE dia WHOLE (Air-Way) from the face, as Brennan builds it (user 2026-10-21 "build it however brennan builds it"): full diameter to the end length - 0.004 - the drill-point height (Brennan FS2408-08 STEP; 120deg drill point not modelled; the -08 rule is ASSUMED for the other sizes); male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-04-04 (both ends; fsmeasure.measure_fsm, group B 2026-10-21); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>Air-Way FF2408 = Brennan p21 on overall length, hex (rounding-only differences count as equal) | Air-Way FF2408 rows are "-O-W/HOLE" (column W/HOLE = a hole dia) - check that OMi's plug is the same | OMi parts file row 5338 (no dimensions) | HOLE DEPTH single-source: full diameter to 0.33 = face-seal end length - 0.004 - the 120deg drill-point height (Brennan FS2408-08 STEP: 0.391, apex 0.500 of 0.504; measured at -08 only - ASSUMED for -04) -&gt; DataStatus ASSUMED</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>FS2408-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>FS2408-06</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.43301</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.252</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="I4" t="n">
+        <v>45</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.27025</v>
+      </c>
+      <c r="L4" t="n">
+        <v>60</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.09701</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.6875</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.03383</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.01562</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.3619</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>FS2408-06</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>ORFS Male Plug (male face seal, blind hole), 11/16-16 UN (male O-ring face seal, SAE J1453) (hollow)</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>FS2408</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>plug head</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11/16-16 UN (male O-ring face seal, SAE J1453)</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>Air-Way FF2408 (s12, double-pass 2026-10-15, parts.air-way.com/api/series/12, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p21 FS2408-06 (ORFS-p021-t02) | MODEL: L24 face -&gt; back face, hex S1 (Air-Way): review table (Air-Way, staged FS table; OMi website list decides the parts); male face-seal end = the straight FSM end library; plug head = hex to a plain flat back face (Brennan FS2408-08 STEP; hex chamfers not modelled); BLIND HOLE dia WHOLE (Air-Way) from the face, as Brennan builds it (user 2026-10-21 "build it however brennan builds it"): full diameter to the end length - 0.004 - the drill-point height (Brennan FS2408-08 STEP; 120deg drill point not modelled; the -08 rule is ASSUMED for the other sizes); male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-06-06 (both ends; fsmeasure.measure_fsm, group B 2026-10-21); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>Air-Way FF2408 (built to Air-Way); Brennan p21 DIFFERS (&lt;= 0.02 in): overall length L24=0.74 vs Brennan L LGTH=0.750 | Air-Way FF2408 rows are "-O-W/HOLE" (column W/HOLE = a hole dia) - check that OMi's plug is the same | OMi parts file row 5339 (no dimensions) | HOLE DEPTH single-source: full diameter to 0.3619 = face-seal end length - 0.004 - the 120deg drill-point height (Brennan FS2408-08 STEP: 0.391, apex 0.500 of 0.504; measured at -08 only - ASSUMED for -06) -&gt; DataStatus ASSUMED</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>FS2408-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>FS2408-10</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.61199</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.276</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.378</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.445</v>
+      </c>
+      <c r="I5" t="n">
+        <v>45</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.419</v>
+      </c>
+      <c r="L5" t="n">
+        <v>60</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.448</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.10598</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.474</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.03866</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.01786</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.4645</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>FS2408-10</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>ORFS Male Plug (male face seal, blind hole), 1-14 UN (male O-ring face seal, SAE J1453) (hollow)</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>FS2408</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>plug head</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>1-14 UN (male O-ring face seal, SAE J1453)</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>Air-Way FF2408 (s12, double-pass 2026-10-15, parts.air-way.com/api/series/12, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p21 FS2408-10 (ORFS-p021-t02) | MODEL: L24 face -&gt; back face, hex S1 (Air-Way): review table (Air-Way, staged FS table; OMi website list decides the parts); male face-seal end = the straight FSM end library; plug head = hex to a plain flat back face (Brennan FS2408-08 STEP; hex chamfers not modelled); BLIND HOLE dia WHOLE (Air-Way) from the face, as Brennan builds it (user 2026-10-21 "build it however brennan builds it"): full diameter to the end length - 0.004 - the drill-point height (Brennan FS2408-08 STEP; 120deg drill point not modelled; the -08 rule is ASSUMED for the other sizes); male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-10-10 (both ends; fsmeasure.measure_fsm, group B 2026-10-21); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>Air-Way FF2408 = Brennan p21 on overall length, hex (rounding-only differences count as equal) | Air-Way FF2408 rows are "-O-W/HOLE" (column W/HOLE = a hole dia) - check that OMi's plug is the same | OMi parts file row 5341 (no dimensions) | HOLE DEPTH single-source: full diameter to 0.4645 = face-seal end length - 0.004 - the 120deg drill-point height (Brennan FS2408-08 STEP: 0.391, apex 0.500 of 0.504; measured at -08 only - ASSUMED for -10) -&gt; DataStatus ASSUMED</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>FS2408-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>FS2408-12</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.7216900000000001</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.3385</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.4405</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.5315</v>
+      </c>
+      <c r="I6" t="n">
+        <v>45</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.59375</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.44855</v>
+      </c>
+      <c r="L6" t="n">
+        <v>60</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.5345</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.12499</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.1875</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.5108</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.4899</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>FS2408-12</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>ORFS Male Plug (male face seal, blind hole), 1 3/16-12 UN (male O-ring face seal, SAE J1453) (hollow)</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>FS2408</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>plug head</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>1 3/16-12 UN (male O-ring face seal, SAE J1453)</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>Air-Way FF2408 (s12, double-pass 2026-10-15, parts.air-way.com/api/series/12, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p21 FS2408-12 (ORFS-p021-t02) | MODEL: L24 face -&gt; back face, hex S1 (Air-Way): review table (Air-Way, staged FS table; OMi website list decides the parts); male face-seal end = the straight FSM end library; plug head = hex to a plain flat back face (Brennan FS2408-08 STEP; hex chamfers not modelled); BLIND HOLE dia WHOLE (Air-Way) from the face, as Brennan builds it (user 2026-10-21 "build it however brennan builds it"): full diameter to the end length - 0.004 - the drill-point height (Brennan FS2408-08 STEP; 120deg drill point not modelled; the -08 rule is ASSUMED for the other sizes); male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-12-12 (both ends; fsmeasure.measure_fsm, group B 2026-10-21); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>Air-Way FF2408 = Brennan p21 on overall length, hex (rounding-only differences count as equal) | Air-Way FF2408 rows are "-O-W/HOLE" (column W/HOLE = a hole dia) - check that OMi's plug is the same | OMi parts file row 5342 (no dimensions) | HOLE DEPTH single-source: full diameter to 0.4899 = face-seal end length - 0.004 - the 120deg drill-point height (Brennan FS2408-08 STEP: 0.391, apex 0.500 of 0.504; measured at -08 only - ASSUMED for -12) -&gt; DataStatus ASSUMED</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>FS2408-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>FS2408-16</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.86603</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.4315</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.5335</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.6565</v>
+      </c>
+      <c r="I7" t="n">
+        <v>45</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.71875</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.46755</v>
+      </c>
+      <c r="L7" t="n">
+        <v>60</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.6595</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.12499</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.4375</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.5298</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.4512</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>FS2408-16</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>ORFS Male Plug (male face seal, blind hole), 1 7/16-12 UN (male O-ring face seal, SAE J1453) (hollow)</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>FS2408</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>plug head</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>1 7/16-12 UN (male O-ring face seal, SAE J1453)</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>Air-Way FF2408 (s12, double-pass 2026-10-15, parts.air-way.com/api/series/12, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p21 FS2408-16 (ORFS-p021-t02) | MODEL: L24 face -&gt; back face, hex S1 (Air-Way): review table (Air-Way, staged FS table; OMi website list decides the parts); male face-seal end = the straight FSM end library; plug head = hex to a plain flat back face (Brennan FS2408-08 STEP; hex chamfers not modelled); BLIND HOLE dia WHOLE (Air-Way) from the face, as Brennan builds it (user 2026-10-21 "build it however brennan builds it"): full diameter to the end length - 0.004 - the drill-point height (Brennan FS2408-08 STEP; 120deg drill point not modelled; the -08 rule is ASSUMED for the other sizes); male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-16-16 (both ends; fsmeasure.measure_fsm, group B 2026-10-21); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>Air-Way FF2408 = Brennan p21 on overall length, hex (rounding-only differences count as equal) | Air-Way FF2408 rows are "-O-W/HOLE" (column W/HOLE = a hole dia) - check that OMi's plug is the same | OMi parts file row 5343 (no dimensions) | HOLE DEPTH single-source: full diameter to 0.4512 = face-seal end length - 0.004 - the 120deg drill-point height (Brennan FS2408-08 STEP: 0.391, apex 0.500 of 0.504; measured at -08 only - ASSUMED for -16) -&gt; DataStatus ASSUMED</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>FS2408-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>FS2408-20</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1.01036</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.5565</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.6585</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.7825</v>
+      </c>
+      <c r="I8" t="n">
+        <v>45</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.84375</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.46855</v>
+      </c>
+      <c r="L8" t="n">
+        <v>60</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.7845</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.12499</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.6875</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.5298</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.3906</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>FS2408-20</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>ORFS Male Plug (male face seal, blind hole), 1 11/16-12 UN (male O-ring face seal, SAE J1453) (hollow)</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>FS2408</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>plug head</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>1 11/16-12 UN (male O-ring face seal, SAE J1453)</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>Air-Way FF2408 (s12, double-pass 2026-10-15, parts.air-way.com/api/series/12, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p21 FS2408-20 (ORFS-p021-t02) | MODEL: L24 face -&gt; back face, hex S1 (Air-Way): review table (Air-Way, staged FS table; OMi website list decides the parts); male face-seal end = the straight FSM end library; plug head = hex to a plain flat back face (Brennan FS2408-08 STEP; hex chamfers not modelled); BLIND HOLE dia WHOLE (Air-Way) from the face, as Brennan builds it (user 2026-10-21 "build it however brennan builds it"): full diameter to the end length - 0.004 - the drill-point height (Brennan FS2408-08 STEP; 120deg drill point not modelled; the -08 rule is ASSUMED for the other sizes); male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-20-20 (both ends; fsmeasure.measure_fsm, group B 2026-10-21); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>Air-Way FF2408 = Brennan p21 on overall length, hex (rounding-only differences count as equal) | Air-Way FF2408 rows are "-O-W/HOLE" (column W/HOLE = a hole dia) - check that OMi's plug is the same | OMi parts file row 5344 (no dimensions) | HOLE DEPTH single-source: full diameter to 0.3906 = face-seal end length - 0.004 - the 120deg drill-point height (Brennan FS2408-08 STEP: 0.391, apex 0.500 of 0.504; measured at -08 only - ASSUMED for -20) -&gt; DataStatus ASSUMED</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>FS2408-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>FS2408-24</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1.22976</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.7125</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.8145</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.9379999999999999</v>
+      </c>
+      <c r="I9" t="n">
+        <v>45</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.4676</v>
+      </c>
+      <c r="L9" t="n">
+        <v>60</v>
+      </c>
+      <c r="M9" t="n">
         <v>0.9405</v>
       </c>
-      <c r="N3" t="n">
+      <c r="N9" t="n">
         <v>0.12505</v>
       </c>
-      <c r="O3" t="n">
+      <c r="O9" t="n">
         <v>2</v>
       </c>
-      <c r="P3" t="n">
+      <c r="P9" t="n">
         <v>0.08333</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="Q9" t="n">
         <v>0.5296</v>
       </c>
-      <c r="R3" t="n">
+      <c r="R9" t="n">
         <v>0.04511</v>
       </c>
-      <c r="S3" t="n">
+      <c r="S9" t="n">
         <v>0.02083</v>
       </c>
-      <c r="T3" t="n">
+      <c r="T9" t="n">
         <v>0.08333</v>
       </c>
-      <c r="U3" t="n">
+      <c r="U9" t="n">
         <v>1.26</v>
       </c>
-      <c r="V3" t="n">
+      <c r="V9" t="n">
         <v>0.3213</v>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>FS2408-24</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>ORFS Male Plug (male face seal, blind hole), 2-12 UN (male O-ring face seal, SAE J1453) (hollow)</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>FS2408</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>plug head</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>2-12 UN (male O-ring face seal, SAE J1453)</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>Air-Way FF2408 (s12, double-pass 2026-10-15, parts.air-way.com/api/series/12, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p21 FS2408-24 (ORFS-p021-t02) | MODEL: L24 face -&gt; back face, hex S1 (Air-Way): review table (Air-Way, staged FS table; OMi website list decides the parts); male face-seal end = the straight FSM end library; plug head = hex to a plain flat back face (Brennan FS2408-08 STEP; hex chamfers not modelled); BLIND HOLE dia WHOLE (Air-Way) from the face, as Brennan builds it (user 2026-10-21 "build it however brennan builds it"): full diameter to the end length - 0.004 - the drill-point height (Brennan FS2408-08 STEP; 120deg drill point not modelled; the -08 rule is ASSUMED for the other sizes); male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-24-24 (both ends; fsmeasure.measure_fsm, orfs_steps2_20261020 ends_survey); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>Air-Way FF2408 (built to Air-Way); Brennan p21 DIFFERS (&lt;= 0.02 in): overall length L24=1.10 vs Brennan L LGTH=1.090 | Air-Way FF2408 rows are "-O-W/HOLE" (column W/HOLE = a hole dia) - check that OMi's plug is the same | OMi parts file row 5345 (no dimensions) | HOLE DEPTH single-source: full diameter to 0.3213 = face-seal end length - 0.004 - the 120deg drill-point height (Brennan FS2408-08 STEP: 0.391, apex 0.500 of 0.504; measured at -08 only - ASSUMED for -24) -&gt; DataStatus ASSUMED</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
+      <c r="AF9" t="inlineStr">
         <is>
           <t>FS2408-24</t>
         </is>

--- a/tools/_out/groupB_20261021/out/fs/DesignTable_FS2408_SW2.xlsx
+++ b/tools/_out/groupB_20261021/out/fs/DesignTable_FS2408_SW2.xlsx
@@ -799,7 +799,7 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>Air-Way FF2408 (s12, double-pass 2026-10-15, parts.air-way.com/api/series/12, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p21 FS2408-04 (ORFS-p021-t02) | MODEL: L24 face -&gt; back face, hex S1 (Air-Way): review table (Air-Way, staged FS table; OMi website list decides the parts); male face-seal end = the straight FSM end library; plug head = hex to a plain flat back face (Brennan FS2408-08 STEP; hex chamfers not modelled); BLIND HOLE dia WHOLE (Air-Way) from the face, as Brennan builds it (user 2026-10-21 "build it however brennan builds it"): full diameter to the end length - 0.004 - the drill-point height (Brennan FS2408-08 STEP; 120deg drill point not modelled; the -08 rule is ASSUMED for the other sizes); male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-04-04 (both ends; fsmeasure.measure_fsm, group B 2026-10-21); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
+          <t>Air-Way FF2408 (s12, double-pass 2026-10-15, parts.air-way.com/api/series/12, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p21 FS2408-04 (ORFS-p021-t02) | MODEL: L24 face -&gt; back face, hex S1 (Air-Way): review table (Air-Way, staged FS table; OMi website list decides the parts); male face-seal end = the straight FSM end library; plug head = hex to a plain flat back face (Brennan FS2408-08 STEP; hex chamfers not modelled); BLIND HOLE dia WHOLE (Air-Way) from the face, as Brennan builds it (user 2026-10-21 "build it however brennan builds it"): full diameter to the end length - 0.004 - the drill-point height (Brennan FS2408-08 STEP; 120deg drill point not modelled; the -08 rule is ASSUMED for the other sizes); male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-04-04 (both ends; fsmeasure.measure_fsm, fsends_20261021); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>Air-Way FF2408 (s12, double-pass 2026-10-15, parts.air-way.com/api/series/12, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p21 FS2408-06 (ORFS-p021-t02) | MODEL: L24 face -&gt; back face, hex S1 (Air-Way): review table (Air-Way, staged FS table; OMi website list decides the parts); male face-seal end = the straight FSM end library; plug head = hex to a plain flat back face (Brennan FS2408-08 STEP; hex chamfers not modelled); BLIND HOLE dia WHOLE (Air-Way) from the face, as Brennan builds it (user 2026-10-21 "build it however brennan builds it"): full diameter to the end length - 0.004 - the drill-point height (Brennan FS2408-08 STEP; 120deg drill point not modelled; the -08 rule is ASSUMED for the other sizes); male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-06-06 (both ends; fsmeasure.measure_fsm, group B 2026-10-21); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
+          <t>Air-Way FF2408 (s12, double-pass 2026-10-15, parts.air-way.com/api/series/12, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p21 FS2408-06 (ORFS-p021-t02) | MODEL: L24 face -&gt; back face, hex S1 (Air-Way): review table (Air-Way, staged FS table; OMi website list decides the parts); male face-seal end = the straight FSM end library; plug head = hex to a plain flat back face (Brennan FS2408-08 STEP; hex chamfers not modelled); BLIND HOLE dia WHOLE (Air-Way) from the face, as Brennan builds it (user 2026-10-21 "build it however brennan builds it"): full diameter to the end length - 0.004 - the drill-point height (Brennan FS2408-08 STEP; 120deg drill point not modelled; the -08 rule is ASSUMED for the other sizes); male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-06-06 (both ends; fsmeasure.measure_fsm, fsends_20261021); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>Air-Way FF2408 (s12, double-pass 2026-10-15, parts.air-way.com/api/series/12, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p21 FS2408-10 (ORFS-p021-t02) | MODEL: L24 face -&gt; back face, hex S1 (Air-Way): review table (Air-Way, staged FS table; OMi website list decides the parts); male face-seal end = the straight FSM end library; plug head = hex to a plain flat back face (Brennan FS2408-08 STEP; hex chamfers not modelled); BLIND HOLE dia WHOLE (Air-Way) from the face, as Brennan builds it (user 2026-10-21 "build it however brennan builds it"): full diameter to the end length - 0.004 - the drill-point height (Brennan FS2408-08 STEP; 120deg drill point not modelled; the -08 rule is ASSUMED for the other sizes); male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-10-10 (both ends; fsmeasure.measure_fsm, group B 2026-10-21); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
+          <t>Air-Way FF2408 (s12, double-pass 2026-10-15, parts.air-way.com/api/series/12, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p21 FS2408-10 (ORFS-p021-t02) | MODEL: L24 face -&gt; back face, hex S1 (Air-Way): review table (Air-Way, staged FS table; OMi website list decides the parts); male face-seal end = the straight FSM end library; plug head = hex to a plain flat back face (Brennan FS2408-08 STEP; hex chamfers not modelled); BLIND HOLE dia WHOLE (Air-Way) from the face, as Brennan builds it (user 2026-10-21 "build it however brennan builds it"): full diameter to the end length - 0.004 - the drill-point height (Brennan FS2408-08 STEP; 120deg drill point not modelled; the -08 rule is ASSUMED for the other sizes); male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-10-10 (both ends; fsmeasure.measure_fsm, fsends_20261021); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>Air-Way FF2408 (s12, double-pass 2026-10-15, parts.air-way.com/api/series/12, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p21 FS2408-12 (ORFS-p021-t02) | MODEL: L24 face -&gt; back face, hex S1 (Air-Way): review table (Air-Way, staged FS table; OMi website list decides the parts); male face-seal end = the straight FSM end library; plug head = hex to a plain flat back face (Brennan FS2408-08 STEP; hex chamfers not modelled); BLIND HOLE dia WHOLE (Air-Way) from the face, as Brennan builds it (user 2026-10-21 "build it however brennan builds it"): full diameter to the end length - 0.004 - the drill-point height (Brennan FS2408-08 STEP; 120deg drill point not modelled; the -08 rule is ASSUMED for the other sizes); male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-12-12 (both ends; fsmeasure.measure_fsm, group B 2026-10-21); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
+          <t>Air-Way FF2408 (s12, double-pass 2026-10-15, parts.air-way.com/api/series/12, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p21 FS2408-12 (ORFS-p021-t02) | MODEL: L24 face -&gt; back face, hex S1 (Air-Way): review table (Air-Way, staged FS table; OMi website list decides the parts); male face-seal end = the straight FSM end library; plug head = hex to a plain flat back face (Brennan FS2408-08 STEP; hex chamfers not modelled); BLIND HOLE dia WHOLE (Air-Way) from the face, as Brennan builds it (user 2026-10-21 "build it however brennan builds it"): full diameter to the end length - 0.004 - the drill-point height (Brennan FS2408-08 STEP; 120deg drill point not modelled; the -08 rule is ASSUMED for the other sizes); male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-12-12 (both ends; fsmeasure.measure_fsm, fsends_20261021); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>Air-Way FF2408 (s12, double-pass 2026-10-15, parts.air-way.com/api/series/12, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p21 FS2408-16 (ORFS-p021-t02) | MODEL: L24 face -&gt; back face, hex S1 (Air-Way): review table (Air-Way, staged FS table; OMi website list decides the parts); male face-seal end = the straight FSM end library; plug head = hex to a plain flat back face (Brennan FS2408-08 STEP; hex chamfers not modelled); BLIND HOLE dia WHOLE (Air-Way) from the face, as Brennan builds it (user 2026-10-21 "build it however brennan builds it"): full diameter to the end length - 0.004 - the drill-point height (Brennan FS2408-08 STEP; 120deg drill point not modelled; the -08 rule is ASSUMED for the other sizes); male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-16-16 (both ends; fsmeasure.measure_fsm, group B 2026-10-21); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
+          <t>Air-Way FF2408 (s12, double-pass 2026-10-15, parts.air-way.com/api/series/12, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p21 FS2408-16 (ORFS-p021-t02) | MODEL: L24 face -&gt; back face, hex S1 (Air-Way): review table (Air-Way, staged FS table; OMi website list decides the parts); male face-seal end = the straight FSM end library; plug head = hex to a plain flat back face (Brennan FS2408-08 STEP; hex chamfers not modelled); BLIND HOLE dia WHOLE (Air-Way) from the face, as Brennan builds it (user 2026-10-21 "build it however brennan builds it"): full diameter to the end length - 0.004 - the drill-point height (Brennan FS2408-08 STEP; 120deg drill point not modelled; the -08 rule is ASSUMED for the other sizes); male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-16-16 (both ends; fsmeasure.measure_fsm, fsends_20261021); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>Air-Way FF2408 (s12, double-pass 2026-10-15, parts.air-way.com/api/series/12, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p21 FS2408-20 (ORFS-p021-t02) | MODEL: L24 face -&gt; back face, hex S1 (Air-Way): review table (Air-Way, staged FS table; OMi website list decides the parts); male face-seal end = the straight FSM end library; plug head = hex to a plain flat back face (Brennan FS2408-08 STEP; hex chamfers not modelled); BLIND HOLE dia WHOLE (Air-Way) from the face, as Brennan builds it (user 2026-10-21 "build it however brennan builds it"): full diameter to the end length - 0.004 - the drill-point height (Brennan FS2408-08 STEP; 120deg drill point not modelled; the -08 rule is ASSUMED for the other sizes); male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-20-20 (both ends; fsmeasure.measure_fsm, group B 2026-10-21); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
+          <t>Air-Way FF2408 (s12, double-pass 2026-10-15, parts.air-way.com/api/series/12, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p21 FS2408-20 (ORFS-p021-t02) | MODEL: L24 face -&gt; back face, hex S1 (Air-Way): review table (Air-Way, staged FS table; OMi website list decides the parts); male face-seal end = the straight FSM end library; plug head = hex to a plain flat back face (Brennan FS2408-08 STEP; hex chamfers not modelled); BLIND HOLE dia WHOLE (Air-Way) from the face, as Brennan builds it (user 2026-10-21 "build it however brennan builds it"): full diameter to the end length - 0.004 - the drill-point height (Brennan FS2408-08 STEP; 120deg drill point not modelled; the -08 rule is ASSUMED for the other sizes); male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-20-20 (both ends; fsmeasure.measure_fsm, fsends_20261021); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
